--- a/artfynd/A 53201-2025 artfynd.xlsx
+++ b/artfynd/A 53201-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>2975495</v>
       </c>
       <c r="B2" t="n">
-        <v>96318</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99103</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>506841.5692176538</v>
+        <v>506842</v>
       </c>
       <c r="R2" t="n">
-        <v>6478788.714184557</v>
+        <v>6478789</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>1993-05-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1995-10-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -796,12 +781,7 @@
         <v>6100305</v>
       </c>
       <c r="B3" t="n">
-        <v>99495</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -833,10 +813,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506841.5692176538</v>
+        <v>506842</v>
       </c>
       <c r="R3" t="n">
-        <v>6478788.714184557</v>
+        <v>6478789</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -866,19 +846,9 @@
           <t>1969-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1969-01-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
